--- a/apps/docs-firefly/Planning.xlsx
+++ b/apps/docs-firefly/Planning.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10709"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andredavcev/Files/Theory/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andredavcev/Files/Theory/apps/docs-firefly/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C4FD65-C991-DD4E-BFA9-9F0D693C1828}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EE5611-8573-8245-93D8-30DC5A730F3A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4440" yWindow="2300" windowWidth="28040" windowHeight="17440" xr2:uid="{F2231EC9-DA71-4148-989E-FDBC3CF37AF6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Chat Rooms</t>
   </si>
@@ -67,6 +67,39 @@
   </si>
   <si>
     <t>TypeDoc</t>
+  </si>
+  <si>
+    <t>Location Alerts</t>
+  </si>
+  <si>
+    <t>Heat Maps</t>
+  </si>
+  <si>
+    <t>Rule Engine</t>
+  </si>
+  <si>
+    <t>Bulk Import</t>
+  </si>
+  <si>
+    <t>Firefly Web</t>
+  </si>
+  <si>
+    <t>API Creation</t>
+  </si>
+  <si>
+    <t>Multimedia Experiences</t>
+  </si>
+  <si>
+    <t>VR</t>
+  </si>
+  <si>
+    <t>Gamification</t>
+  </si>
+  <si>
+    <t>Event Alerts</t>
+  </si>
+  <si>
+    <t>iFrame Components</t>
   </si>
 </sst>
 </file>
@@ -110,9 +143,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -427,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{524B1229-E4D2-9B46-AA28-82821AD184A9}">
-  <dimension ref="B2:C11"/>
+  <dimension ref="B2:C22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -443,16 +477,16 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>0</v>
+      <c r="B3" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>1</v>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
@@ -460,7 +494,7 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -468,32 +502,87 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
